--- a/0_Threshold_OUTPUT_REPORT/0_best_conclusion_data.xlsx
+++ b/0_Threshold_OUTPUT_REPORT/0_best_conclusion_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V69"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,15 +526,20 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Inverted_Pval</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Alignment</t>
         </is>
@@ -590,7 +595,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.4887</v>
+        <v>0.5412</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -624,13 +629,18 @@
           <t>GCGAAGAAAAGGCGAACA</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
         <v>0.02978808476609356</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>0.9702119152339065</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -686,7 +696,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3555</v>
+        <v>0.4206</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -720,13 +730,18 @@
           <t>CGAACAAAAACCGAACA</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
         <v>0.1105557776889244</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.8894442223110756</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -782,7 +797,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.4464</v>
+        <v>0.5158</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -816,13 +831,18 @@
           <t>TTGTTTTGTT</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
         <v>0.6271491403438625</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -878,7 +898,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2829</v>
+        <v>0.3333</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -912,13 +932,18 @@
           <t>CGAACATATGTTCG</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -974,7 +999,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.2823</v>
+        <v>0.344</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1004,13 +1029,18 @@
           <t>TTACACAGTAA</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
         <v>0.06597361055577769</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>0.9340263894442223</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1066,7 +1096,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.2762</v>
+        <v>0.2933</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1096,13 +1126,18 @@
           <t>CTGTTTTTTTATACAG</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
         <v>0.003398640543782487</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>0.9966013594562175</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1158,7 +1193,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.3148</v>
+        <v>0.3172</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1192,13 +1227,18 @@
           <t>TAACGCTCTGTTAA</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
         <v>0.03738504598160736</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>0.9626149540183926</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -1254,7 +1294,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.8571</v>
+        <v>0.8919</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1284,13 +1324,18 @@
           <t>ATGTTCTCGTTATGTTCT</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
         <v>0.001599360255897641</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0.9984006397441023</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1346,7 +1391,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.6919</v>
+        <v>0.7211</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1380,13 +1425,18 @@
           <t>TTAATGTCCGGTTAACC</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
         <v>0.003998400639744102</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>0.9960015993602559</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1442,7 +1492,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.341</v>
+        <v>0.3458</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1472,13 +1522,18 @@
           <t>TCGAACATATGTTCGA</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1534,7 +1589,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.5513</v>
+        <v>0.6073</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1564,13 +1619,18 @@
           <t>TGATTGTAACTTCGATCA</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
         <v>0.2542982806877249</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0.745701719312275</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1626,7 +1686,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.326</v>
+        <v>0.3743</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1656,13 +1716,18 @@
           <t>TGTGATCTACATCACA</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1718,7 +1783,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.1955</v>
+        <v>0.2112</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1752,13 +1817,18 @@
           <t>AGAACAAGTGTTCT</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
         <v>0.005997600959616154</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0.9940023990403839</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1814,7 +1884,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.2268</v>
+        <v>0.2498</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1848,13 +1918,18 @@
           <t>AGAACAAATGTTCT</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1910,7 +1985,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.2706</v>
+        <v>0.291</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1944,13 +2019,18 @@
           <t>GACTGTTTTTTTGTACAGTC</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2006,7 +2086,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.5169</v>
+        <v>0.5281</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2040,13 +2120,18 @@
           <t>TACTGTATTTATATACAGTA</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2102,7 +2187,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.8723</v>
+        <v>0.9082</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -2132,13 +2217,18 @@
           <t>TACATTGAGCAGGATCAAAAAA</t>
         </is>
       </c>
-      <c r="T18" t="n">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2194,7 +2284,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1.1175</v>
+        <v>1.0897</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -2224,13 +2314,18 @@
           <t>TTGTTAAAAAAATGTTAA</t>
         </is>
       </c>
-      <c r="T19" t="n">
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
         <v>0.004398240703718513</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>0.9956017592962815</v>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2286,7 +2381,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.8663</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2316,13 +2411,18 @@
           <t>TGTGATCGATATCACA</t>
         </is>
       </c>
-      <c r="T20" t="n">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2378,7 +2478,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1.606</v>
+        <v>1.5854</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2412,13 +2512,18 @@
           <t>TCTTGTTTATATTTTGTTTATAT</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
         <v>0.002798880447820872</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>0.9972011195521792</v>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2474,7 +2579,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.5808</v>
+        <v>0.6136</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2508,13 +2613,18 @@
           <t>TGTTTAGGGTTTGTTTA</t>
         </is>
       </c>
-      <c r="T22" t="n">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
         <v>0.02998800479808077</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>0.9700119952019193</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2570,7 +2680,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.351</v>
+        <v>0.3875</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2604,13 +2714,18 @@
           <t>TGCTCAAAGGGGCA</t>
         </is>
       </c>
-      <c r="T23" t="n">
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
         <v>0.2309076369452219</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>0.7690923630547781</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2666,7 +2781,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.3156</v>
+        <v>0.3199</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2700,13 +2815,18 @@
           <t>GGTTGACACATGTAAACC</t>
         </is>
       </c>
-      <c r="T24" t="n">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2762,7 +2882,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.3857</v>
+        <v>0.3921</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -2792,13 +2912,18 @@
           <t>CTGTACATCAATACAG</t>
         </is>
       </c>
-      <c r="T25" t="n">
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
         <v>0.005597760895641743</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>0.9944022391043582</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2854,7 +2979,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.3493</v>
+        <v>0.408</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2884,13 +3009,18 @@
           <t>TTTGAAATTCAAA</t>
         </is>
       </c>
-      <c r="T26" t="n">
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
         <v>0.02159136345461815</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>0.9784086365453818</v>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2946,7 +3076,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.186</v>
+        <v>0.2512</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2980,13 +3110,18 @@
           <t>TTTGCTATACAAA</t>
         </is>
       </c>
-      <c r="T27" t="n">
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
         <v>0.2249100359856057</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.7750899640143942</v>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3042,7 +3177,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.7155</v>
+        <v>0.6369</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -3072,13 +3207,18 @@
           <t>ATAAGAACATATGTTCGTTT</t>
         </is>
       </c>
-      <c r="T28" t="n">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3134,7 +3274,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.492</v>
+        <v>0.5094</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3168,13 +3308,18 @@
           <t>ACCTAATAAAAATAAGGT</t>
         </is>
       </c>
-      <c r="T29" t="n">
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3230,7 +3375,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.1778</v>
+        <v>0.1818</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3264,13 +3409,18 @@
           <t>AACACATGTT</t>
         </is>
       </c>
-      <c r="T30" t="n">
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
         <v>0.1273490603758497</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>0.8726509396241503</v>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3326,7 +3476,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.1607</v>
+        <v>0.218</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3360,13 +3510,18 @@
           <t>GAACAGGTGTTC</t>
         </is>
       </c>
-      <c r="T31" t="n">
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
         <v>0.00699720111955218</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.9930027988804478</v>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3422,7 +3577,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.2284</v>
+        <v>0.2291</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3456,13 +3611,18 @@
           <t>CGAACAGGTGTTCG</t>
         </is>
       </c>
-      <c r="T32" t="n">
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3518,7 +3678,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.6558</v>
+        <v>0.6741</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -3548,13 +3708,18 @@
           <t>TATCGAACACATGTTCGATA</t>
         </is>
       </c>
-      <c r="T33" t="n">
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3610,7 +3775,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.3363</v>
+        <v>0.3908</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -3640,13 +3805,18 @@
           <t>AAAAGCCCGT</t>
         </is>
       </c>
-      <c r="T34" t="n">
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
         <v>0.8338664534186325</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.1661335465813675</v>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3702,7 +3872,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.4708</v>
+        <v>0.3467</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -3732,13 +3902,18 @@
           <t>GTATCATATGATAC</t>
         </is>
       </c>
-      <c r="T35" t="n">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3794,7 +3969,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.3221</v>
+        <v>0.3373</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -3824,13 +3999,18 @@
           <t>TAGTACTTATGTACTA</t>
         </is>
       </c>
-      <c r="T36" t="n">
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
         <v>0.002998800479808077</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>0.9970011995201919</v>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -3886,7 +4066,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.3211</v>
+        <v>0.3402</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3920,13 +4100,18 @@
           <t>GAACAACACAGGAAC</t>
         </is>
       </c>
-      <c r="T37" t="n">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
         <v>0.07856857257097161</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>0.9214314274290284</v>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3982,7 +4167,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.5309</v>
+        <v>0.534</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -4012,13 +4197,18 @@
           <t>ACTGTATAAATATACAGT</t>
         </is>
       </c>
-      <c r="T38" t="n">
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4074,7 +4264,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.4954</v>
+        <v>0.5327</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -4104,13 +4294,18 @@
           <t>CTGTCACACAACTGTCA</t>
         </is>
       </c>
-      <c r="T39" t="n">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4166,7 +4361,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.6959</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -4196,13 +4391,18 @@
           <t>ACTGGATATATATACAGT</t>
         </is>
       </c>
-      <c r="T40" t="n">
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4258,7 +4458,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.4304</v>
+        <v>0.2982</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -4288,13 +4488,18 @@
           <t>TTGATCCAGATCAA</t>
         </is>
       </c>
-      <c r="T41" t="n">
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
         <v>0.001799280287884846</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4350,7 +4555,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.3135</v>
+        <v>0.3985</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4384,13 +4589,18 @@
           <t>TTTTTTT</t>
         </is>
       </c>
-      <c r="T42" t="n">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
         <v>0.01199520191923231</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>0.9880047980807677</v>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4446,7 +4656,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.3</v>
+        <v>0.331</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4480,13 +4690,18 @@
           <t>GTATCACCCCGGATAC</t>
         </is>
       </c>
-      <c r="T43" t="n">
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4542,7 +4757,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.2828</v>
+        <v>0.3454</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -4572,13 +4787,18 @@
           <t>GAACAAGACCGGAAC</t>
         </is>
       </c>
-      <c r="T44" t="n">
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
         <v>0.00739704118352659</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>0.9926029588164734</v>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4634,7 +4854,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.7661</v>
+        <v>0.8253</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4668,13 +4888,18 @@
           <t>CAGAACACGCGCAGAACAA</t>
         </is>
       </c>
-      <c r="T45" t="n">
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
         <v>0.1145541783286685</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.8854458216713315</v>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4730,7 +4955,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.3239</v>
+        <v>0.3811</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4764,13 +4989,18 @@
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T46" t="n">
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
         <v>0.08756497401039584</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>0.9124350259896041</v>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4826,7 +5056,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.4208</v>
+        <v>0.4766</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -4860,13 +5090,18 @@
           <t>GAACACAGGACGAAC</t>
         </is>
       </c>
-      <c r="T47" t="n">
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -4922,7 +5157,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.3439</v>
+        <v>0.3616</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -4952,13 +5187,18 @@
           <t>AACGCTCCCGAAAC</t>
         </is>
       </c>
-      <c r="T48" t="n">
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
         <v>0.02618952419032387</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.9738104758096762</v>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5014,7 +5254,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1.6398</v>
+        <v>1.6046</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
@@ -5044,13 +5284,18 @@
           <t>TTTGTTTAGATTTTGTTTA</t>
         </is>
       </c>
-      <c r="T49" t="n">
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
         <v>0.003198720511795282</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>0.9968012794882047</v>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5106,7 +5351,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.9127</v>
+        <v>0.3963</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -5136,13 +5381,18 @@
           <t>GTTAATTAAATGTTA</t>
         </is>
       </c>
-      <c r="T50" t="n">
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
         <v>0.1541383446621351</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>0.8458616553378648</v>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5198,7 +5448,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.3686</v>
+        <v>0.3281</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -5228,13 +5478,18 @@
           <t>TTCATAATTTTTCATA</t>
         </is>
       </c>
-      <c r="T51" t="n">
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
         <v>0.01039584166333467</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>0.9896041583366654</v>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5290,7 +5545,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.7892</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -5320,13 +5575,18 @@
           <t>ATGTTCTTGATTTGTTCT</t>
         </is>
       </c>
-      <c r="T52" t="n">
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
         <v>0.031187524990004</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>0.968812475009996</v>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5382,7 +5642,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.2504</v>
+        <v>0.3153</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -5412,13 +5672,18 @@
           <t>CGAACATATGTTCG</t>
         </is>
       </c>
-      <c r="T53" t="n">
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5474,7 +5739,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.3109</v>
+        <v>0.3333</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -5504,13 +5769,18 @@
           <t>TGTGATCAAGATCACA</t>
         </is>
       </c>
-      <c r="T54" t="n">
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5566,7 +5836,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.8655</v>
+        <v>0.9092</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -5596,13 +5866,18 @@
           <t>GTGACATAGATCAC</t>
         </is>
       </c>
-      <c r="T55" t="n">
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
         <v>0.01359456217512995</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>0.98640543782487</v>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5658,7 +5933,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.7443</v>
+        <v>0.8026</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -5688,13 +5963,18 @@
           <t>ACTGTATAAATAAACAGT</t>
         </is>
       </c>
-      <c r="T56" t="n">
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5750,7 +6030,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.2335</v>
+        <v>0.3391</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -5780,13 +6060,18 @@
           <t>GTGCGCCAAATCAC</t>
         </is>
       </c>
-      <c r="T57" t="n">
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
         <v>0.5715713714514195</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>0.4284286285485805</v>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5842,7 +6127,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.2036</v>
+        <v>0.2253</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -5872,13 +6157,18 @@
           <t>ATCAATC</t>
         </is>
       </c>
-      <c r="T58" t="n">
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
         <v>0.5983606557377049</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5934,7 +6224,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>1.2783</v>
+        <v>1.3056</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
@@ -5964,13 +6254,18 @@
           <t>ATGTGATCACTATCACAA</t>
         </is>
       </c>
-      <c r="T59" t="n">
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
         <v>0.23390643742503</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>0.7660935625749701</v>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6026,7 +6321,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.183</v>
+        <v>0.2004</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -6060,13 +6355,18 @@
           <t>TGTACAAATGTACA</t>
         </is>
       </c>
-      <c r="T60" t="n">
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
         <v>0.003798480607756897</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>0.9962015193922431</v>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6122,7 +6422,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.3469</v>
+        <v>0.4013</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -6152,13 +6452,18 @@
           <t>GGTGCGCTTCACCGCACC</t>
         </is>
       </c>
-      <c r="T61" t="n">
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
         <v>0.01239504198320672</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>0.9876049580167933</v>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6214,7 +6519,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.7185</v>
+        <v>0.764</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -6244,13 +6549,18 @@
           <t>TGTGAACCTCCCCACA</t>
         </is>
       </c>
-      <c r="T62" t="n">
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
         <v>0.002598960415833667</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
         <v>0.9974010395841664</v>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6306,7 +6616,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0.3478</v>
+        <v>0.3674</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -6340,13 +6650,18 @@
           <t>TTAGTAAAAATACTAA</t>
         </is>
       </c>
-      <c r="T63" t="n">
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
         <v>0.003198720511795282</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>0.9968012794882047</v>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6402,7 +6717,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.5448</v>
+        <v>0.6031</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -6436,13 +6751,18 @@
           <t>TTTAATTATTGTTTAT</t>
         </is>
       </c>
-      <c r="T64" t="n">
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
         <v>0.008996401439424231</v>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
         <v>0.9910035985605757</v>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6498,7 +6818,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>1.0305</v>
+        <v>1.0561</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -6528,13 +6848,18 @@
           <t>ATATGTGATTTAGATCACATTT</t>
         </is>
       </c>
-      <c r="T65" t="n">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6590,7 +6915,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1.3298</v>
+        <v>0.8002</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -6624,13 +6949,18 @@
           <t>CTGTTTATAATTTGTTTA</t>
         </is>
       </c>
-      <c r="T66" t="n">
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
         <v>0.005997600959616154</v>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
         <v>0.9940023990403839</v>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6686,7 +7016,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.6869</v>
+        <v>0.7363</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -6716,13 +7046,18 @@
           <t>CAAGGTGTTAGATTG</t>
         </is>
       </c>
-      <c r="T67" t="n">
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6778,7 +7113,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>1.1164</v>
+        <v>1.17</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -6808,13 +7143,18 @@
           <t>ATACACTTTGTAACATTTT</t>
         </is>
       </c>
-      <c r="T68" t="n">
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
         <v>0.1391443422630948</v>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
         <v>0.8608556577369052</v>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6870,7 +7210,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.6187</v>
+        <v>0.7104</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -6900,13 +7240,18 @@
           <t>CAAAATGTTAA</t>
         </is>
       </c>
-      <c r="T69" t="n">
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
         <v>0.2990803678528589</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>0.7009196321471411</v>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
